--- a/DirectX/Bin/Asset/Brotato/tables/WeaponSetBonus.xlsx
+++ b/DirectX/Bin/Asset/Brotato/tables/WeaponSetBonus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jglee\ASTR\AstrDX\DirectX\Bin\Asset\Brotato\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C60902-DED0-480E-95DC-77F48C0D65EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536F3D5E-B20A-4D07-9CB4-556887E77825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{D120B664-9625-4DC7-9A8C-DD4CF0EBB165}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>Precise</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1147,10 +1151,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F041C6E9-5782-4583-B661-038F00A20FAE}">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1158,67 +1162,70 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1226,55 +1233,55 @@
         <v>6</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>6</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>4</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>6</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>5</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>4</v>
       </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
       <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
         <v>4</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>3</v>
-      </c>
-      <c r="S2">
-        <v>4</v>
       </c>
       <c r="T2">
         <v>4</v>
@@ -1282,11 +1289,14 @@
       <c r="U2">
         <v>4</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2">
+        <v>4</v>
+      </c>
+      <c r="W2" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1294,263 +1304,278 @@
         <v>4</v>
       </c>
       <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>13</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>13</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
       <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
         <v>13</v>
       </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
       <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
         <v>13</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>3</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>15</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>-2</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>15</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>-4</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>15</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>-6</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>15</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>-8</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>15</v>
       </c>
-      <c r="V3" s="1">
+      <c r="W3" s="1">
         <v>-10</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
       </c>
       <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>8</v>
       </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>8</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>8</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>4</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>5</v>
       </c>
-      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>14</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>14</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>18</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>14</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>24</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>14</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>30</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>13</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>-1</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>13</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>-2</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>13</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>-3</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>13</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>-4</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>13</v>
       </c>
-      <c r="V5" s="1">
+      <c r="W5" s="1">
         <v>-5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
         <v>24</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>24</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>24</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>15</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>24</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>20</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>24</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>25</v>
       </c>
-      <c r="V6" s="1"/>
-      <c r="X6">
+      <c r="W6" s="1"/>
+      <c r="Y6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>12</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>12</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>30</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>12</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>40</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>12</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>50</v>
       </c>
-      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1559,88 +1584,94 @@
         <v>5</v>
       </c>
       <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
         <v>10</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>15</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>5</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>20</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>5</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>25</v>
       </c>
-      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
         <v>-20</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
         <v>-40</v>
       </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
       <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
         <v>-60</v>
       </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
       <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
         <v>-80</v>
       </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" s="1">
         <v>-100</v>
       </c>
-      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>256</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10">
+        <v>256</v>
+      </c>
+      <c r="D10">
         <v>3</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>3</v>
       </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -1649,321 +1680,348 @@
         <v>3</v>
       </c>
       <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
         <v>4</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>3</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>5</v>
       </c>
-      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>512</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11">
+        <v>512</v>
+      </c>
+      <c r="D11">
         <v>13</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>13</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>13</v>
       </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
       <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
         <v>13</v>
       </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
       <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
         <v>13</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>3</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>14</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>3</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>14</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>3</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>14</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>6</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>14</v>
       </c>
-      <c r="V11" s="1">
+      <c r="W11" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1024</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12">
+        <v>1024</v>
+      </c>
+      <c r="D12">
         <v>16</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>16</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>16</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>15</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>16</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>20</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>16</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>25</v>
       </c>
-      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
         <v>2048</v>
       </c>
-      <c r="B13" t="s">
-        <v>2</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="V13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="W13" s="1"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>4096</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>37</v>
       </c>
       <c r="C14">
+        <v>4096</v>
+      </c>
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>10</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>6</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>10</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>9</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>10</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>12</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>10</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>15</v>
       </c>
-      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>8192</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
         <v>6</v>
       </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
       <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
         <v>9</v>
       </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
       <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
         <v>12</v>
       </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15" s="1">
         <v>15</v>
       </c>
-      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>16384</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16">
+        <v>16384</v>
+      </c>
+      <c r="D16">
         <v>17</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>5</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>17</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>10</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>17</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>15</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>17</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>20</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>17</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>25</v>
       </c>
-      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>32768</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
+        <v>32768</v>
+      </c>
+      <c r="D17">
         <v>11</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>11</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
       <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
         <v>11</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>3</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>11</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>4</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>11</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>5</v>
       </c>
-      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>65536</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
+        <v>65536</v>
+      </c>
+      <c r="D18">
         <v>14</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>14</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>6</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>14</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>9</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>14</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>12</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>14</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>15</v>
       </c>
-      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
